--- a/artfynd/A 12572-2026 artfynd.xlsx
+++ b/artfynd/A 12572-2026 artfynd.xlsx
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132880715</v>
+        <v>132880450</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,30 +1441,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1472,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758712</v>
+        <v>758598</v>
       </c>
       <c r="R9" t="n">
-        <v>7176550</v>
+        <v>7176539</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,13 +1511,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1535,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132880450</v>
+        <v>132880715</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,31 +1551,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758598</v>
+        <v>758712</v>
       </c>
       <c r="R10" t="n">
-        <v>7176539</v>
+        <v>7176550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,17 +1620,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
